--- a/utils/monday_sprint_sprint_2023-02.xlsx
+++ b/utils/monday_sprint_sprint_2023-02.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="145">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>6466</t>
+    <t>1407235050</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>20/06/2021</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>19/01/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,13 +102,13 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>6223</t>
+    <t>1407235089</t>
   </si>
   <si>
     <t>Inclusão de campo no apontamento de Inspeção</t>
   </si>
   <si>
-    <t>16083</t>
+    <t>3325428328</t>
   </si>
   <si>
     <t>Análise</t>
@@ -123,13 +123,16 @@
     <t>04/10/2022</t>
   </si>
   <si>
+    <t>25/01/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Outubro</t>
   </si>
   <si>
-    <t>14430</t>
+    <t>3383334936</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -141,7 +144,10 @@
     <t>17/10/2022</t>
   </si>
   <si>
-    <t>16877</t>
+    <t>28/01/2023</t>
+  </si>
+  <si>
+    <t>3534231556</t>
   </si>
   <si>
     <t>Novo Recurso</t>
@@ -159,7 +165,7 @@
     <t>Novembro</t>
   </si>
   <si>
-    <t>17122</t>
+    <t>3619317191</t>
   </si>
   <si>
     <t>Campo OC  na consulta de SICs do projeto</t>
@@ -174,7 +180,7 @@
     <t>Dezembro</t>
   </si>
   <si>
-    <t>17758</t>
+    <t>3756352739</t>
   </si>
   <si>
     <t>Criar tabela tipo de categoria de compra e campo FK combo box</t>
@@ -183,22 +189,37 @@
     <t>05/01/2023</t>
   </si>
   <si>
+    <t>29/01/2023</t>
+  </si>
+  <si>
     <t>Janeiro</t>
   </si>
   <si>
+    <t>3756359800</t>
+  </si>
+  <si>
     <t>Alteração do fluxo de aprovação</t>
   </si>
   <si>
+    <t>3756369227</t>
+  </si>
+  <si>
     <t>Segregação de SICs por tipo e prazo de resolução para acompanhamento:</t>
   </si>
   <si>
+    <t>3756380893</t>
+  </si>
+  <si>
     <t>Descrições e motivos SIC Web</t>
   </si>
   <si>
+    <t>3756389057</t>
+  </si>
+  <si>
     <t>Inclusão do campo Frete Especial</t>
   </si>
   <si>
-    <t>17995</t>
+    <t>3807277393</t>
   </si>
   <si>
     <t>Inclusão de informação de modelo na CPC</t>
@@ -207,61 +228,70 @@
     <t>13/01/2023</t>
   </si>
   <si>
+    <t>26/01/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>17908</t>
+    <t>3808256079</t>
   </si>
   <si>
     <t>Data do último fornecimento para o setor 500 no relatório de sequências em aberto por setor</t>
   </si>
   <si>
-    <t>8918</t>
+    <t>3808291453</t>
   </si>
   <si>
     <t>Análise de discrepâncias de informações ERP x Qlik</t>
   </si>
   <si>
-    <t>17958</t>
+    <t>3808300959</t>
   </si>
   <si>
     <t>Relatório de Custeio - Apontamentos MOLDAGEM USE/ULE e MACHARIA</t>
   </si>
   <si>
-    <t>17956</t>
+    <t>3808313654</t>
   </si>
   <si>
     <t>Relatório de Custeio - Apontamentos MOLDAGEM CARROSSEL</t>
   </si>
   <si>
-    <t>17935</t>
+    <t>3808341275</t>
   </si>
   <si>
     <t>Novo filtro na tela de Estatística de Movimentação</t>
   </si>
   <si>
-    <t>17860</t>
+    <t>3808370487</t>
   </si>
   <si>
     <t>Nova tela para programação de modelos</t>
   </si>
   <si>
+    <t>3808426968</t>
+  </si>
+  <si>
     <t>Inclusão de motivo de refugo do peso refugado no relatório de Produção</t>
   </si>
   <si>
-    <t>17913</t>
+    <t>3808432065</t>
   </si>
   <si>
     <t>Alteração do Formato do Arquivo de Procedimento de Usinagem</t>
   </si>
   <si>
-    <t>17851</t>
+    <t>23/01/2023</t>
+  </si>
+  <si>
+    <t>3808481194</t>
   </si>
   <si>
     <t>Atualização de relatório de Follow Up</t>
   </si>
   <si>
-    <t>17710</t>
+    <t>3808488550</t>
   </si>
   <si>
     <t>Atualização de versão</t>
@@ -270,13 +300,13 @@
     <t>Migrar o relatório de estatísticas mensais para EV3</t>
   </si>
   <si>
-    <t>17562</t>
+    <t>3808496150</t>
   </si>
   <si>
     <t>Disparo automático de OC para fornecedores</t>
   </si>
   <si>
-    <t>TBD</t>
+    <t>3814040768</t>
   </si>
   <si>
     <t>Centralizar login do adm no executável de gerenciador de documentos</t>
@@ -285,7 +315,7 @@
     <t>16/01/2023</t>
   </si>
   <si>
-    <t>17574</t>
+    <t>3815721650</t>
   </si>
   <si>
     <t>Apontamento de acabamento corte/escarfa</t>
@@ -306,7 +336,7 @@
     <t>3817140295</t>
   </si>
   <si>
-    <t>18054</t>
+    <t>3831110328</t>
   </si>
   <si>
     <t>Relatório - Bloqueio SIC</t>
@@ -315,15 +345,15 @@
     <t>18/01/2023</t>
   </si>
   <si>
-    <t>18085</t>
+    <t>22/01/2023</t>
+  </si>
+  <si>
+    <t>3876263371</t>
   </si>
   <si>
     <t>Adequação da tela de apontamento</t>
   </si>
   <si>
-    <t>26/01/2023</t>
-  </si>
-  <si>
     <t>Semana 4</t>
   </si>
   <si>
@@ -333,7 +363,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-02</t>
+    <t>Jun/2021</t>
   </si>
   <si>
     <t>Base</t>
@@ -397,6 +427,9 @@
   </si>
   <si>
     <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Fazendo</t>
@@ -1022,7 +1055,7 @@
         <v>35</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1031,30 +1064,30 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>34</v>
@@ -1066,10 +1099,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1081,42 +1114,42 @@
         <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1128,12 +1161,12 @@
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1145,13 +1178,13 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>21</v>
@@ -1160,10 +1193,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1172,15 +1205,15 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1192,10 +1225,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -1207,10 +1240,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1219,15 +1252,15 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1239,10 +1272,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -1254,10 +1287,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1266,15 +1299,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1286,10 +1319,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -1301,10 +1334,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1313,15 +1346,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1333,10 +1366,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -1348,10 +1381,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1360,15 +1393,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1380,10 +1413,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -1395,10 +1428,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1407,15 +1440,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1427,10 +1460,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -1442,10 +1475,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1454,15 +1487,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1474,13 +1507,13 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>21</v>
@@ -1489,10 +1522,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1501,15 +1534,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1521,13 +1554,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>21</v>
@@ -1536,7 +1569,7 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>24</v>
@@ -1548,45 +1581,45 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1595,15 +1628,15 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1615,60 +1648,60 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="O17" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1677,10 +1710,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1689,33 +1722,33 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>21</v>
@@ -1724,10 +1757,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1736,33 +1769,33 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>21</v>
@@ -1771,10 +1804,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1783,15 +1816,15 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1803,13 +1836,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1818,10 +1851,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1830,15 +1863,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1850,10 +1883,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1865,10 +1898,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1877,33 +1910,33 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>21</v>
@@ -1912,10 +1945,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1924,15 +1957,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1944,13 +1977,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -1959,10 +1992,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1971,15 +2004,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -1991,13 +2024,13 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -2006,10 +2039,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2021,12 +2054,12 @@
         <v>27</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2038,10 +2071,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -2053,10 +2086,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2068,30 +2101,30 @@
         <v>27</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2100,10 +2133,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2115,30 +2148,30 @@
         <v>27</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2147,10 +2180,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2162,30 +2195,30 @@
         <v>27</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2194,10 +2227,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2209,12 +2242,12 @@
         <v>27</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2226,13 +2259,13 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>21</v>
@@ -2241,10 +2274,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2256,12 +2289,12 @@
         <v>27</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2273,13 +2306,13 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>21</v>
@@ -2288,10 +2321,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2300,10 +2333,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2319,23 +2352,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2343,16 +2376,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2363,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>61.53</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2371,7 +2404,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2384,7 +2417,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2392,7 +2425,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2423,12 +2456,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -2442,7 +2475,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2452,25 +2485,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2487,13 +2520,13 @@
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2505,15 +2538,15 @@
         <v>30</v>
       </c>
       <c r="P10" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -2531,16 +2564,16 @@
         <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="Q11">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -2557,65 +2590,59 @@
         <v>3</v>
       </c>
       <c r="J12" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>138</v>
       </c>
       <c r="Q12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H13">
         <v>13</v>
       </c>
       <c r="M13" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
     </row>
     <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H14">
         <v>5</v>
       </c>
       <c r="M14" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2623,13 +2650,13 @@
     </row>
     <row r="15" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D15" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2637,7 +2664,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2645,7 +2672,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2653,10 +2680,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2664,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2672,142 +2699,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
